--- a/sample_data/Testfile1.xlsx
+++ b/sample_data/Testfile1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DataCombiner\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91305415-A505-461D-9CA0-8DB26B2509A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13C535F-1C6F-4ECF-BC97-E21A172E4B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/sample_data/Testfile1.xlsx
+++ b/sample_data/Testfile1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DataCombiner\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13C535F-1C6F-4ECF-BC97-E21A172E4B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E53F54-C361-4824-A7BE-5AA7415167D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6915" yWindow="5205" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -382,7 +382,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">

--- a/sample_data/Testfile1.xlsx
+++ b/sample_data/Testfile1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DataCombiner\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E53F54-C361-4824-A7BE-5AA7415167D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF1EBD-5F3F-4146-AFCD-5E8134B861B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="5205" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>NAMES</t>
   </si>
   <si>
-    <t>ATTEND?</t>
-  </si>
-  <si>
     <t>JOSH</t>
   </si>
   <si>
@@ -45,10 +42,7 @@
     <t>KAIHAN</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>N</t>
+    <t>phone</t>
   </si>
 </sst>
 </file>
@@ -374,39 +368,39 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
